--- a/office/data/高考成绩.xlsx
+++ b/office/data/高考成绩.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\glpla.github.io\office\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839177DB-C353-4ECD-96E6-EA39063CE52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BABFD0E-A581-4C8C-88F6-B3288C12BF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="高考成绩" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,14 +163,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
@@ -203,7 +195,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -508,392 +502,398 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="9.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="3" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>90</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>68</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>90</v>
       </c>
-      <c r="F2" s="1">
-        <f>C2+D2+E2</f>
+      <c r="F2">
+        <f t="shared" ref="F2:F18" si="0">C2+D2+E2</f>
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>96</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>92</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>97</v>
       </c>
-      <c r="F3" s="1">
-        <f>C3+D3+E3</f>
+      <c r="F3">
+        <f t="shared" si="0"/>
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>68</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>95</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>96</v>
       </c>
-      <c r="F4" s="1">
-        <f>C4+D4+E4</f>
+      <c r="F4">
+        <f t="shared" si="0"/>
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>78</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>78</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>92</v>
       </c>
-      <c r="F5" s="1">
-        <f>C5+D5+E5</f>
+      <c r="F5">
+        <f t="shared" si="0"/>
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>75</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>79</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>97</v>
       </c>
-      <c r="F6" s="1">
-        <f>C6+D6+E6</f>
+      <c r="F6">
+        <f t="shared" si="0"/>
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>87</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>87</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>95</v>
       </c>
-      <c r="F7" s="1">
-        <f>C7+D7+E7</f>
+      <c r="F7">
+        <f t="shared" si="0"/>
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>85</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>87</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>98</v>
       </c>
-      <c r="F8" s="1">
-        <f>C8+D8+E8</f>
+      <c r="F8">
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>75</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>76</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>93</v>
       </c>
-      <c r="F9" s="1">
-        <f>C9+D9+E9</f>
+      <c r="F9">
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>88</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>78</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>90</v>
       </c>
-      <c r="F10" s="1">
-        <f>C10+D10+E10</f>
+      <c r="F10">
+        <f t="shared" si="0"/>
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>96</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>86</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>93</v>
       </c>
-      <c r="F11" s="1">
-        <f>C11+D11+E11</f>
+      <c r="F11">
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>95</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>84</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>95</v>
       </c>
-      <c r="F12" s="1">
-        <f>C12+D12+E12</f>
+      <c r="F12">
+        <f t="shared" si="0"/>
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>90</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>86</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>91</v>
       </c>
-      <c r="F13" s="1">
-        <f>C13+D13+E13</f>
+      <c r="F13">
+        <f t="shared" si="0"/>
         <v>267</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>86</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>83</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>93</v>
       </c>
-      <c r="F14" s="1">
-        <f>C14+D14+E14</f>
+      <c r="F14">
+        <f t="shared" si="0"/>
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>86</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>80</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>92</v>
       </c>
-      <c r="F15" s="1">
-        <f>C15+D15+E15</f>
+      <c r="F15">
+        <f t="shared" si="0"/>
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>98</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>93</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>96</v>
       </c>
-      <c r="F16" s="1">
-        <f>C16+D16+E16</f>
+      <c r="F16">
+        <f t="shared" si="0"/>
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>97</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>94</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>96</v>
       </c>
-      <c r="F17" s="1">
-        <f>C17+D17+E17</f>
+      <c r="F17">
+        <f t="shared" si="0"/>
         <v>287</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>96</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>93</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>98</v>
       </c>
-      <c r="F18" s="1">
-        <f>C18+D18+E18</f>
+      <c r="F18">
+        <f t="shared" si="0"/>
         <v>287</v>
       </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -905,7 +905,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -915,7 +915,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
